--- a/config/SpEffect.xlsx
+++ b/config/SpEffect.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\20636.DESKTOP-Q1SUICL\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB86C9F-27AE-44A8-8BF7-913CB947D240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1D70EE-D0AF-478D-8377-0FE4CB69CFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="510" yWindow="1440" windowWidth="24075" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1695" yWindow="1560" windowWidth="24075" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RoleSp" sheetId="1" r:id="rId1"/>
-    <sheet name="RoleSpList" sheetId="2" r:id="rId2"/>
+    <sheet name="SpList" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="85">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -103,205 +103,257 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>jisi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0010</t>
+  </si>
+  <si>
+    <t>attribute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0013_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hou</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0014</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>change</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>window</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>star</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0019</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skeleton</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>huoyan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jianxue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reduce attack</t>
+  </si>
+  <si>
+    <t>shield</t>
+  </si>
+  <si>
+    <t>skill_0005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文件名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0006</t>
+  </si>
+  <si>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>skill_0006_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shouji1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0006_2</t>
+  </si>
+  <si>
+    <t>shouji2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤出场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>科技护盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即死</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>群体强化升级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抗伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>换位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交换属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圣光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>转移伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0013_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单体强化升级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>群体增强特效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff特效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能生效特效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0002|skill_0005|skill_0025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>skill_0009</t>
-  </si>
-  <si>
-    <t>jisi</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_0010</t>
-  </si>
-  <si>
-    <t>attribute</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_0013_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>qian</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hou</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_0014</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>change</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>skill_0015</t>
-  </si>
-  <si>
-    <t>weak</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>skill_0016</t>
-  </si>
-  <si>
-    <t>window</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>skill_0017</t>
-  </si>
-  <si>
-    <t>star</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_0019</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skeleton</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_0022</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>huoyan</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>skill_0023</t>
-  </si>
-  <si>
-    <t>Slash</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_0025</t>
-  </si>
-  <si>
-    <t>jianxue</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>skill_0026</t>
-  </si>
-  <si>
-    <t>Reduce attack</t>
-  </si>
-  <si>
-    <t>skill_0002</t>
-  </si>
-  <si>
-    <t>shield</t>
-  </si>
-  <si>
-    <t>skill_0005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文件名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_0006</t>
-  </si>
-  <si>
-    <t>damage</t>
-  </si>
-  <si>
-    <t>skill_0006_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>shouji1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_0006_2</t>
-  </si>
-  <si>
-    <t>shouji2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>召唤出场</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>护盾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>科技护盾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>即死</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>群体强化升级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>抗伤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>换位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交换属性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>流血</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_0027</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>圣光</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_0024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>转移伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_0013_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单体强化升级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_0003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_0009|skill_0013_1|skill_0013_2|skill_0014|skill_0015|skill_0016|skill_0017|skill_0019|skill_0022|skill_0023|skill_0024|skill_0026|skill_0027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到虚弱buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intensifierColony</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>checkSkill</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -367,17 +419,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -659,59 +711,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5" style="3" customWidth="1"/>
     <col min="2" max="2" width="26.625" style="3" customWidth="1"/>
     <col min="3" max="3" width="28.25" style="3" customWidth="1"/>
     <col min="4" max="4" width="31.375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="26.125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="26.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="46.625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="E1" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="1" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="E2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
+      <c r="E3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
         <v>100001</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -720,9 +802,18 @@
       <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+      <c r="E4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
         <v>100002</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -731,9 +822,18 @@
       <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
+      <c r="E5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
         <v>100003</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -742,9 +842,18 @@
       <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
+      <c r="E6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
         <v>100004</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -753,9 +862,18 @@
       <c r="C7" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
+      <c r="E7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
         <v>100005</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -764,9 +882,18 @@
       <c r="C8" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
+      <c r="E8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
         <v>100006</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -775,9 +902,18 @@
       <c r="C9" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
+      <c r="E9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
         <v>100007</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -786,9 +922,18 @@
       <c r="C10" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
+      <c r="E10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
         <v>100008</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -797,9 +942,18 @@
       <c r="C11" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
+      <c r="E11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
         <v>100009</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -808,9 +962,18 @@
       <c r="C12" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
+      <c r="E12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
         <v>100010</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -819,9 +982,18 @@
       <c r="C13" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
+      <c r="E13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
         <v>100011</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -830,9 +1002,18 @@
       <c r="C14" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
+      <c r="E14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
         <v>100012</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -841,9 +1022,18 @@
       <c r="C15" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
+      <c r="E15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
         <v>100013</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -852,9 +1042,18 @@
       <c r="C16" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
+      <c r="E16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
         <v>100014</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -863,9 +1062,18 @@
       <c r="C17" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
+      <c r="E17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
         <v>100015</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -874,9 +1082,18 @@
       <c r="C18" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
+      <c r="E18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
         <v>100016</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -885,9 +1102,18 @@
       <c r="C19" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
+      <c r="E19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
         <v>100017</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -896,9 +1122,18 @@
       <c r="C20" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
+      <c r="E20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
         <v>100018</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -907,9 +1142,18 @@
       <c r="C21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
+      <c r="E21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
         <v>100019</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -918,9 +1162,18 @@
       <c r="C22" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
+      <c r="E22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
         <v>100020</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -929,9 +1182,18 @@
       <c r="C23" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
+      <c r="E23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
         <v>100021</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -940,9 +1202,18 @@
       <c r="C24" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
+      <c r="E24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A25" s="3">
         <v>100022</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -951,9 +1222,18 @@
       <c r="C25" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
+      <c r="E25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A26" s="3">
         <v>100023</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -962,9 +1242,18 @@
       <c r="C26" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
+      <c r="E26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A27" s="3">
         <v>100024</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -973,9 +1262,18 @@
       <c r="C27" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
+      <c r="E27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A28" s="3">
         <v>100025</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -984,9 +1282,18 @@
       <c r="C28" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
+      <c r="E28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
         <v>100026</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -995,9 +1302,18 @@
       <c r="C29" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
+      <c r="E29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
         <v>100027</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -1006,9 +1322,18 @@
       <c r="C30" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="1">
+      <c r="E30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
         <v>100028</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -1017,9 +1342,18 @@
       <c r="C31" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="1">
+      <c r="E31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
         <v>100029</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -1028,9 +1362,18 @@
       <c r="C32" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="1">
+      <c r="E32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
         <v>100030</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -1039,9 +1382,18 @@
       <c r="C33" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="1">
+      <c r="E33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
         <v>100031</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -1050,9 +1402,18 @@
       <c r="C34" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="1">
+      <c r="E34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
         <v>100032</v>
       </c>
       <c r="B35" s="3" t="s">
@@ -1061,9 +1422,18 @@
       <c r="C35" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="1">
+      <c r="E35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
         <v>100033</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -1072,9 +1442,18 @@
       <c r="C36" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="1">
+      <c r="E36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A37" s="3">
         <v>100034</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -1083,9 +1462,18 @@
       <c r="C37" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="1">
+      <c r="E37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A38" s="3">
         <v>100035</v>
       </c>
       <c r="B38" s="3" t="s">
@@ -1094,9 +1482,18 @@
       <c r="C38" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="1">
+      <c r="E38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A39" s="3">
         <v>100036</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -1105,9 +1502,18 @@
       <c r="C39" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="1">
+      <c r="E39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A40" s="3">
         <v>100037</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -1116,9 +1522,18 @@
       <c r="C40" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="1">
+      <c r="E40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A41" s="3">
         <v>100038</v>
       </c>
       <c r="B41" s="3" t="s">
@@ -1127,9 +1542,18 @@
       <c r="C41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="1">
+      <c r="E41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A42" s="3">
         <v>100039</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -1138,9 +1562,18 @@
       <c r="C42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="1">
+      <c r="E42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A43" s="3">
         <v>100040</v>
       </c>
       <c r="B43" s="3" t="s">
@@ -1149,9 +1582,18 @@
       <c r="C43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="1">
+      <c r="E43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A44" s="3">
         <v>100041</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -1160,9 +1602,18 @@
       <c r="C44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="1">
+      <c r="E44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A45" s="3">
         <v>100042</v>
       </c>
       <c r="B45" s="3" t="s">
@@ -1171,9 +1622,18 @@
       <c r="C45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" s="1">
+      <c r="E45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A46" s="3">
         <v>100043</v>
       </c>
       <c r="B46" s="3" t="s">
@@ -1182,9 +1642,18 @@
       <c r="C46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="1">
+      <c r="E46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A47" s="3">
         <v>100044</v>
       </c>
       <c r="B47" s="3" t="s">
@@ -1193,9 +1662,18 @@
       <c r="C47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="1">
+      <c r="E47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A48" s="3">
         <v>100045</v>
       </c>
       <c r="B48" s="3" t="s">
@@ -1204,9 +1682,18 @@
       <c r="C48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="1">
+      <c r="E48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A49" s="3">
         <v>100046</v>
       </c>
       <c r="B49" s="3" t="s">
@@ -1215,9 +1702,18 @@
       <c r="C49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" s="1">
+      <c r="E49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A50" s="3">
         <v>100047</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -1226,9 +1722,18 @@
       <c r="C50" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" s="1">
+      <c r="E50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A51" s="3">
         <v>100048</v>
       </c>
       <c r="B51" s="3" t="s">
@@ -1237,9 +1742,18 @@
       <c r="C51" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52" s="1">
+      <c r="E51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
         <v>100049</v>
       </c>
       <c r="B52" s="3" t="s">
@@ -1248,9 +1762,18 @@
       <c r="C52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53" s="1">
+      <c r="E52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A53" s="3">
         <v>100050</v>
       </c>
       <c r="B53" s="3" t="s">
@@ -1259,9 +1782,18 @@
       <c r="C53" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54" s="1">
+      <c r="E53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A54" s="3">
         <v>100051</v>
       </c>
       <c r="B54" s="3" t="s">
@@ -1270,9 +1802,18 @@
       <c r="C54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55" s="1">
+      <c r="E54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A55" s="3">
         <v>100052</v>
       </c>
       <c r="B55" s="3" t="s">
@@ -1281,9 +1822,18 @@
       <c r="C55" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56" s="1">
+      <c r="E55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A56" s="3">
         <v>100053</v>
       </c>
       <c r="B56" s="3" t="s">
@@ -1292,9 +1842,18 @@
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A57" s="1">
+      <c r="E56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="3">
         <v>100054</v>
       </c>
       <c r="B57" s="3" t="s">
@@ -1302,11 +1861,21 @@
       </c>
       <c r="C57" s="3" t="s">
         <v>16</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1315,10 +1884,10 @@
   <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="14.125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="15.375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="14.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.625" style="2" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="10.375" customWidth="1"/>
     <col min="7" max="8" width="11.125" customWidth="1"/>
@@ -1328,332 +1897,335 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="5" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
         <v>13</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="B16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="B17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
         <v>17</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="B20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
-        <v>2</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="5" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="5" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>21</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>22</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
-        <v>5</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="C25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
-        <v>6</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="5">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="5">
-        <v>8</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="5">
-        <v>9</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="5">
-        <v>10</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="5">
-        <v>11</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="5">
-        <v>12</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="5">
-        <v>13</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="5">
-        <v>14</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="5">
-        <v>15</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="5">
-        <v>16</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="5">
-        <v>17</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="5">
-        <v>18</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="5">
-        <v>19</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="5">
-        <v>20</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="5">
-        <v>21</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="5">
-        <v>22</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
